--- a/Registros manuales.xlsx
+++ b/Registros manuales.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\GERENTE DE PROYECTOS\Proyecto Choriboni\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Fabrica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1ABC2D-9301-4E87-8DEB-4E3F60089FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="25-mar" sheetId="1" r:id="rId1"/>
     <sheet name="26-mar" sheetId="2" r:id="rId2"/>
     <sheet name="GASTOS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>3 chorizos</t>
   </si>
@@ -61,23 +60,51 @@
     <t>GASTOS</t>
   </si>
   <si>
-    <t>papa</t>
-  </si>
-  <si>
     <t>VENTAS</t>
+  </si>
+  <si>
+    <t>CASINO: Melón, Guayaba</t>
+  </si>
+  <si>
+    <t>MATERIA PRIMA: Bulto de papa</t>
+  </si>
+  <si>
+    <t>MATERIA PRIMA: Pan perro</t>
+  </si>
+  <si>
+    <t>unidades</t>
+  </si>
+  <si>
+    <t>precio unidad</t>
+  </si>
+  <si>
+    <t>precio empaque</t>
+  </si>
+  <si>
+    <t>EPS: Pastas y cura</t>
+  </si>
+  <si>
+    <t>MERCADO: cebolla, aji, bolsas negras</t>
+  </si>
+  <si>
+    <t>CASINO: Leche</t>
+  </si>
+  <si>
+    <t>SERVICIOS: Luz</t>
+  </si>
+  <si>
+    <t>gastos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +137,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -130,20 +169,21 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Millares" xfId="1" builtinId="3"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Incorrecto" xfId="2" builtinId="27"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -421,13 +461,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -468,7 +508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2115A65-2775-489A-8962-3612C5383BF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -477,7 +517,7 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -508,32 +548,138 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D081AB-72B3-40AF-89B3-0BC378321FE1}">
-  <dimension ref="A4:C8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="4">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4">
+        <f>+SUM(C7:C12)</f>
+        <v>168803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="4">
+        <f>+C3-C4</f>
+        <v>131197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46106</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C8" s="5">
-        <v>20000</v>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4">
+        <v>12000</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>17000</v>
+      </c>
+      <c r="D9">
+        <v>8500</v>
+      </c>
+      <c r="E9">
+        <f>+D9/6</f>
+        <v>1416.6666666666667</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4">
+        <v>39803</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>46109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>46109</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>46109</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4">
+        <v>160150</v>
       </c>
     </row>
   </sheetData>

--- a/Registros manuales.xlsx
+++ b/Registros manuales.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="25-mar" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="GASTOS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Registros manuales.xlsx
+++ b/Registros manuales.xlsx
@@ -17,7 +17,6 @@
     <sheet name="GASTOS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>3 chorizos</t>
   </si>
@@ -95,6 +94,12 @@
   </si>
   <si>
     <t>gastos</t>
+  </si>
+  <si>
+    <t>MERCADO: platano limòn</t>
+  </si>
+  <si>
+    <t>CASINO: 2 bolsas de agua</t>
   </si>
 </sst>
 </file>
@@ -550,7 +555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -559,127 +564,152 @@
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="4">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
       <c r="C3" s="4">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
+        <f>+SUM(C6:C12)</f>
+        <v>193803</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C4" s="4">
-        <f>+SUM(C7:C12)</f>
-        <v>168803</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C5" s="4">
-        <f>+C3-C4</f>
-        <v>131197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <f>+C2-C3</f>
+        <v>106197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>46107</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4">
-        <v>12000</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6">
+        <v>17000</v>
+      </c>
+      <c r="E8">
+        <v>8500</v>
+      </c>
+      <c r="F8">
+        <f>+E8/6</f>
+        <v>1416.6666666666667</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>46107</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>17000</v>
-      </c>
-      <c r="D9">
-        <v>8500</v>
-      </c>
-      <c r="E9">
-        <f>+D9/6</f>
-        <v>1416.6666666666667</v>
-      </c>
-      <c r="F9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4">
+        <v>39803</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="4">
-        <v>39803</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46109</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
+        <v>46110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>46110</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>46109</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>46109</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C16" s="4">
         <v>160150</v>
       </c>
     </row>

--- a/Registros manuales.xlsx
+++ b/Registros manuales.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Fabrica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\GERENTE DE PROYECTOS\Proyecto Choriboni\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26924B61-9E43-40AD-8B98-D7A44723D382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="20370" yWindow="-2070" windowWidth="21840" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25-mar" sheetId="1" r:id="rId1"/>
     <sheet name="26-mar" sheetId="2" r:id="rId2"/>
-    <sheet name="GASTOS" sheetId="3" r:id="rId3"/>
+    <sheet name="REGISTROS" sheetId="4" r:id="rId3"/>
+    <sheet name="GASTOS" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>3 chorizos</t>
   </si>
@@ -100,17 +102,58 @@
   </si>
   <si>
     <t>CASINO: 2 bolsas de agua</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>20 CHORIZOS CRUDOS</t>
+  </si>
+  <si>
+    <t>NEQUI</t>
+  </si>
+  <si>
+    <t>EFEC</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>chorizos</t>
+  </si>
+  <si>
+    <t>gaseosas</t>
+  </si>
+  <si>
+    <t>2 chorizos</t>
+  </si>
+  <si>
+    <t>2 chorizos + gaseosa</t>
+  </si>
+  <si>
+    <t>1 gaseosa  + chorizo</t>
+  </si>
+  <si>
+    <t>chorizo</t>
+  </si>
+  <si>
+    <t>2 chorizo con arepa y 1 chorizo solo</t>
+  </si>
+  <si>
+    <t>3 chorizos + hit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,8 +193,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,8 +230,37 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -172,13 +268,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -186,14 +293,33 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
+    <cellStyle name="Bueno" xfId="4" builtinId="26"/>
     <cellStyle name="Incorrecto" xfId="2" builtinId="27"/>
+    <cellStyle name="Millares" xfId="3" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FF66FFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -467,7 +593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -514,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -554,7 +680,230 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28DAEAEB-9B66-489D-944F-8CF3924FF6F9}">
+  <dimension ref="B3:F30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="10">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4">
+        <f>16000+7000</f>
+        <v>23000</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4">
+        <v>16000</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="4">
+        <v>19000</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="16">
+        <v>28500</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4">
+        <v>11000</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4">
+        <v>11000</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4">
+        <v>8000</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C15" s="16">
+        <f>+SUMIF($D$7:$D$13,D15,$C$7:$C$13)</f>
+        <v>86500</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="15">
+        <f>+SUMIF($D$7:$D$13,D16,$C$7:$C$13)</f>
+        <v>30000</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="14">
+        <f>+C15+C16</f>
+        <v>116500</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="10">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="4">
+        <v>64000</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="4">
+        <v>12000</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="14">
+        <f>+C21+C22</f>
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="10">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="9">
+        <f>4500*20</f>
+        <v>90000</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>3500</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Registros manuales.xlsx
+++ b/Registros manuales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\GERENTE DE PROYECTOS\Proyecto Choriboni\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26924B61-9E43-40AD-8B98-D7A44723D382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B955CA-7A5D-43E9-8766-77E403E5FC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-2070" windowWidth="21840" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,8 @@
     <sheet name="25-mar" sheetId="1" r:id="rId1"/>
     <sheet name="26-mar" sheetId="2" r:id="rId2"/>
     <sheet name="REGISTROS" sheetId="4" r:id="rId3"/>
-    <sheet name="GASTOS" sheetId="3" r:id="rId4"/>
+    <sheet name="productos" sheetId="5" r:id="rId4"/>
+    <sheet name="GASTOS" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="58">
   <si>
     <t>3 chorizos</t>
   </si>
@@ -141,6 +142,78 @@
   </si>
   <si>
     <t>3 chorizos + hit</t>
+  </si>
+  <si>
+    <t>degustación</t>
+  </si>
+  <si>
+    <t>10 gaseosa</t>
+  </si>
+  <si>
+    <t>cerveza</t>
+  </si>
+  <si>
+    <t>pan hambu</t>
+  </si>
+  <si>
+    <t>mercado</t>
+  </si>
+  <si>
+    <t>hit</t>
+  </si>
+  <si>
+    <t>mercado: acite, agua, servilletas</t>
+  </si>
+  <si>
+    <t>uber</t>
+  </si>
+  <si>
+    <t>MATERIA PRIMA: Filete de pechuga - AVICOLA</t>
+  </si>
+  <si>
+    <t>chorizo con papa</t>
+  </si>
+  <si>
+    <t>Un</t>
+  </si>
+  <si>
+    <t>producto</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>coca cola</t>
+  </si>
+  <si>
+    <t>carne de 30,000</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>AJUSTE CONTABLE</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>DaviPlata</t>
+  </si>
+  <si>
+    <t>descuento</t>
+  </si>
+  <si>
+    <t>chorizo CRUDO</t>
+  </si>
+  <si>
+    <t>carne de 40,000</t>
+  </si>
+  <si>
+    <t>aguacate</t>
+  </si>
+  <si>
+    <t>fruta</t>
   </si>
 </sst>
 </file>
@@ -151,9 +224,9 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,8 +290,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,6 +339,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -285,7 +371,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -295,7 +381,7 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -304,6 +390,19 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bueno" xfId="4" builtinId="26"/>
@@ -329,6 +428,191 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>231912</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>48932</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>567239</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>46749</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{486DD0EC-4479-A480-FCF5-3921DFEA16CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="15155" t="6446" r="17790" b="1349"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8915189" y="4087742"/>
+          <a:ext cx="3045817" cy="5288327"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>803412</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>149090</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>331304</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>57978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72C8EDC6-9CC5-01AF-0AAD-57E88E26FD11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect l="8780" t="5788" r="21552" b="7494"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7392230" y="8907946"/>
+          <a:ext cx="3528388" cy="5855805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>305500</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>91111</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>645406</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>49698</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8807080-4CFD-1D92-69A9-86D6D78A2776}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect l="6439" t="5279" r="17142" b="5546"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="6617804" y="17437442"/>
+          <a:ext cx="2816087" cy="4377041"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>66258</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>165650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>630715</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>41415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0742342-83E5-E89D-8466-306EB81970D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect l="23883" t="1899" r="24489" b="15592"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="6713669" y="13056913"/>
+          <a:ext cx="2161765" cy="4606370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -681,22 +965,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28DAEAEB-9B66-489D-944F-8CF3924FF6F9}">
-  <dimension ref="B3:F30"/>
+  <dimension ref="A3:H121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.85546875" customWidth="1"/>
+    <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
@@ -704,7 +992,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>32</v>
       </c>
@@ -716,7 +1004,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>28</v>
       </c>
@@ -729,8 +1017,9 @@
       <c r="E8" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>29</v>
       </c>
@@ -743,8 +1032,9 @@
       <c r="E9" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="17" t="s">
         <v>33</v>
       </c>
@@ -757,8 +1047,9 @@
       <c r="E10" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>30</v>
       </c>
@@ -769,7 +1060,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>30</v>
       </c>
@@ -780,7 +1071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>31</v>
       </c>
@@ -791,10 +1082,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C15" s="16">
         <f>+SUMIF($D$7:$D$13,D15,$C$7:$C$13)</f>
         <v>86500</v>
@@ -803,7 +1094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C16" s="15">
         <f>+SUMIF($D$7:$D$13,D16,$C$7:$C$13)</f>
         <v>30000</v>
@@ -812,13 +1103,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C17" s="14">
         <f>+C15+C16</f>
         <v>116500</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>21</v>
       </c>
@@ -826,7 +1117,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>26</v>
       </c>
@@ -839,8 +1130,9 @@
       <c r="E21" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>27</v>
       </c>
@@ -853,14 +1145,15 @@
       <c r="E22" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="13"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C24" s="14">
         <f>+C21+C22</f>
         <v>76000</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>21</v>
       </c>
@@ -868,7 +1161,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>22</v>
       </c>
@@ -882,8 +1175,9 @@
       <c r="E29" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>3</v>
       </c>
@@ -895,6 +1189,1164 @@
       </c>
       <c r="E30" s="13" t="s">
         <v>25</v>
+      </c>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="10">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="9">
+        <f>8000*25</f>
+        <v>200000</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36">
+        <v>47000</v>
+      </c>
+      <c r="H36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <f>3*0</f>
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>16000</v>
+      </c>
+      <c r="H37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <f>10*3000</f>
+        <v>30000</v>
+      </c>
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <v>27000</v>
+      </c>
+      <c r="D40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <f>4500*2</f>
+        <v>9000</v>
+      </c>
+      <c r="D41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="18">
+        <f>+SUM(C36:C41)</f>
+        <v>266000</v>
+      </c>
+      <c r="G43" s="18">
+        <f>+SUM(G36:G41)</f>
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C50" s="10">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" s="4">
+        <f>+C53*VLOOKUP(B53,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>40</v>
+      </c>
+      <c r="H53">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" s="4">
+        <f>+C54*VLOOKUP(B54,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" t="s">
+        <v>41</v>
+      </c>
+      <c r="H54">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" s="4">
+        <f>+C55*VLOOKUP(B55,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" s="4">
+        <f>+C56*VLOOKUP(B56,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" s="4">
+        <f>+C57*VLOOKUP(B57,productos!A:B,2,0)</f>
+        <v>24000</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58" s="4">
+        <f>+C58*VLOOKUP(B58,productos!A:B,2,0)</f>
+        <v>9000</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>4</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1</v>
+      </c>
+      <c r="D59" s="19">
+        <f>+C59*VLOOKUP(B59,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>4</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1</v>
+      </c>
+      <c r="D60" s="19">
+        <f>+C60*VLOOKUP(B60,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>5</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="19">
+        <f>+C61*VLOOKUP(B61,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>5</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1</v>
+      </c>
+      <c r="D62" s="19">
+        <f>+C62*VLOOKUP(B62,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>6</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1</v>
+      </c>
+      <c r="D63" s="19">
+        <f>+C63*VLOOKUP(B63,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>7</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" s="7">
+        <v>2</v>
+      </c>
+      <c r="D64" s="19">
+        <f>+C64*VLOOKUP(B64,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64">
+        <v>349000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>8</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" s="7">
+        <v>2</v>
+      </c>
+      <c r="D65" s="19">
+        <f>+C65*VLOOKUP(B65,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65">
+        <v>308750</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>9</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="7">
+        <v>1</v>
+      </c>
+      <c r="D66" s="19">
+        <f>+C66*VLOOKUP(B66,productos!A:B,2,0)</f>
+        <v>30000</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66">
+        <f>+G64-G65</f>
+        <v>40250</v>
+      </c>
+      <c r="H66" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>9</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="7">
+        <v>2</v>
+      </c>
+      <c r="D67" s="19">
+        <f>+C67*VLOOKUP(B67,productos!A:B,2,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D70" s="14">
+        <f>+SUM(D53:D68)</f>
+        <v>161000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C73" s="10">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76" s="4">
+        <f>+C76*VLOOKUP(B76,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" s="4">
+        <f>+C77*VLOOKUP(B77,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78" t="s">
+        <v>43</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78" s="4">
+        <f>+C78*VLOOKUP(B78,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79" s="4">
+        <f>+C79*VLOOKUP(B79,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80" s="4">
+        <f>+C80*VLOOKUP(B80,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81" s="4">
+        <f>+C81*VLOOKUP(B81,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" s="4">
+        <f>+C83*VLOOKUP(B83,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>4</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" s="4">
+        <f>+C84*VLOOKUP(B84,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E84" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>5</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" s="4">
+        <f>+C85*VLOOKUP(B85,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="D86" s="4">
+        <f>+C86*VLOOKUP(B86,productos!A:B,2,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D88" s="22">
+        <f>+SUM(D76:D86)</f>
+        <v>87000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C90" s="10">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93" t="s">
+        <v>43</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" s="4">
+        <f>+C93*VLOOKUP(B93,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" t="s">
+        <v>56</v>
+      </c>
+      <c r="H93" s="4">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>1</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" s="4">
+        <f>+C94*VLOOKUP(B94,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" t="s">
+        <v>57</v>
+      </c>
+      <c r="H94" s="15">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" s="24">
+        <v>-1000</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="4">
+        <f>+H93+H94</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" s="4">
+        <f>+C96*VLOOKUP(B96,productos!A:B,2,0)</f>
+        <v>16000</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97" s="4">
+        <f>+C97*VLOOKUP(B97,productos!A:B,2,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>3</v>
+      </c>
+      <c r="B98" t="s">
+        <v>54</v>
+      </c>
+      <c r="C98">
+        <v>4</v>
+      </c>
+      <c r="D98" s="4">
+        <f>+C98*VLOOKUP(B98,productos!A:B,2,0)</f>
+        <v>18000</v>
+      </c>
+      <c r="E98" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>54</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" s="4">
+        <f>+C99*VLOOKUP(B99,productos!A:B,2,0)</f>
+        <v>9000</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" s="4">
+        <f>+C100*VLOOKUP(B100,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>6</v>
+      </c>
+      <c r="B101" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" s="4">
+        <f>+C101*VLOOKUP(B101,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E101" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>7</v>
+      </c>
+      <c r="B102" t="s">
+        <v>43</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102" s="4">
+        <f>+C102*VLOOKUP(B102,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103" t="s">
+        <v>48</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103" s="4">
+        <f>+C103*VLOOKUP(B103,productos!A:B,2,0)</f>
+        <v>30000</v>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>9</v>
+      </c>
+      <c r="B104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" s="16">
+        <f>+C104*VLOOKUP(B104,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>10</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105" s="16">
+        <v>16000</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>11</v>
+      </c>
+      <c r="B106" t="s">
+        <v>55</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106" s="4">
+        <f>+C106*VLOOKUP(B106,productos!A:B,2,0)</f>
+        <v>40000</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>12</v>
+      </c>
+      <c r="B107" t="s">
+        <v>43</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" s="4">
+        <f>+C107*VLOOKUP(B107,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>13</v>
+      </c>
+      <c r="B108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108" s="25">
+        <f>+C108*VLOOKUP(B108,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E108" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>14</v>
+      </c>
+      <c r="B109" t="s">
+        <v>43</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109" s="25">
+        <f>+C109*VLOOKUP(B109,productos!A:B,2,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E109" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+      <c r="D110" s="25">
+        <f>+C110*VLOOKUP(B110,productos!A:B,2,0)</f>
+        <v>32000</v>
+      </c>
+      <c r="E110" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D111" s="25"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>8</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" s="4">
+        <f>+C112*VLOOKUP(B112,productos!A:B,2,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="E112" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>15</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+      <c r="D113" s="4">
+        <f>+C113*VLOOKUP(B113,productos!A:B,2,0)</f>
+        <v>9000</v>
+      </c>
+      <c r="E113" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>12</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" s="4">
+        <f>+C114*VLOOKUP(B114,productos!A:B,2,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="E114" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>14</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" s="4">
+        <f>+C115*VLOOKUP(B115,productos!A:B,2,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="E115" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D116" s="25"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D117" s="25">
+        <f>+SUMIF($E$93:$E$110,E117,$D$93:$D$110)</f>
+        <v>104000</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D118" s="26">
+        <f>+SUMIF($E$93:$E$110,E118,$D$93:$D$110)</f>
+        <v>129000</v>
+      </c>
+      <c r="E118" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G118" s="14">
+        <f>+SUM(D106:D110,D93:D104)</f>
+        <v>217000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="D119" s="25">
+        <f>+D117+D118</f>
+        <v>233000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D121" s="22">
+        <f>+SUM(D112:D115)+D119</f>
+        <v>257000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AE74F6-30D3-4848-AF85-46D4DD635803}">
+  <dimension ref="A10:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>40000</v>
       </c>
     </row>
   </sheetData>
@@ -902,9 +2354,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -913,17 +2365,17 @@
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C2" s="4">
         <v>300000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
@@ -932,13 +2384,13 @@
         <v>193803</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="4">
         <f>+C2-C3</f>
         <v>106197</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>46106</v>
       </c>
@@ -949,7 +2401,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46107</v>
       </c>
@@ -969,7 +2421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>46107</v>
       </c>
@@ -990,7 +2442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>46107</v>
       </c>
@@ -1001,7 +2453,7 @@
         <v>39803</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>46109</v>
       </c>
@@ -1012,7 +2464,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46109</v>
       </c>
@@ -1023,7 +2475,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>46110</v>
       </c>
@@ -1034,7 +2486,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>46110</v>
       </c>
@@ -1045,13 +2497,16 @@
         <v>9900</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>46109</v>
       </c>
@@ -1060,6 +2515,18 @@
       </c>
       <c r="C16" s="4">
         <v>160150</v>
+      </c>
+      <c r="G16">
+        <v>29952</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <f>+G15-G16</f>
+        <v>16398</v>
       </c>
     </row>
   </sheetData>

--- a/Registros manuales.xlsx
+++ b/Registros manuales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\GERENTE DE PROYECTOS\Proyecto Choriboni\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026_Dark Kitchen\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B955CA-7A5D-43E9-8766-77E403E5FC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BC5DE3-D98D-4EF3-99CC-F7B4AE0140E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-2070" windowWidth="21840" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-2070" windowWidth="21840" windowHeight="13140" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25-mar" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="68">
   <si>
     <t>3 chorizos</t>
   </si>
@@ -214,19 +214,50 @@
   </si>
   <si>
     <t>fruta</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>111 012 6615</t>
+  </si>
+  <si>
+    <t>gaseosaS</t>
+  </si>
+  <si>
+    <t>EFECTIVO</t>
+  </si>
+  <si>
+    <t>PARRILLADAS</t>
+  </si>
+  <si>
+    <t>fruver</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>arepas</t>
+  </si>
+  <si>
+    <t>compras</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,8 +328,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u val="singleAccounting"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,8 +401,31 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -363,15 +442,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -403,12 +492,32 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="9" borderId="2" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="0" xfId="5" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Bueno" xfId="4" builtinId="26"/>
     <cellStyle name="Incorrecto" xfId="2" builtinId="27"/>
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -965,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28DAEAEB-9B66-489D-944F-8CF3924FF6F9}">
-  <dimension ref="A3:H121"/>
+  <dimension ref="A3:I340"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
@@ -2196,7 +2305,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>15</v>
       </c>
@@ -2214,7 +2323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>12</v>
       </c>
@@ -2232,7 +2341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>14</v>
       </c>
@@ -2250,10 +2359,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D116" s="25"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D117" s="25">
         <f>+SUMIF($E$93:$E$110,E117,$D$93:$D$110)</f>
         <v>104000</v>
@@ -2262,7 +2371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D118" s="26">
         <f>+SUMIF($E$93:$E$110,E118,$D$93:$D$110)</f>
         <v>129000</v>
@@ -2275,16 +2384,1301 @@
         <v>217000</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="D119" s="25">
         <f>+D117+D118</f>
         <v>233000</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D121" s="22">
         <f>+SUM(D112:D115)+D119</f>
         <v>257000</v>
+      </c>
+      <c r="I121" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C126" s="10">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>43</v>
+      </c>
+      <c r="C129">
+        <v>15</v>
+      </c>
+      <c r="D129" s="25">
+        <f>+C129*VLOOKUP(B129,productos!A:B,2,0)</f>
+        <v>120000</v>
+      </c>
+      <c r="E129" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>1</v>
+      </c>
+      <c r="B130" t="s">
+        <v>47</v>
+      </c>
+      <c r="C130">
+        <v>15</v>
+      </c>
+      <c r="D130" s="26">
+        <f>+C130*VLOOKUP(B130,productos!A:B,2,0)</f>
+        <v>45000</v>
+      </c>
+      <c r="E130" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D132" s="14">
+        <f>+D129+D130</f>
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C135" s="10">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D137" s="27">
+        <f>+SUM(D140:D147)</f>
+        <v>142700</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" s="27">
+        <v>11000</v>
+      </c>
+      <c r="E140" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141" s="27">
+        <v>1700</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142" s="27">
+        <v>18000</v>
+      </c>
+      <c r="E142" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>3</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" s="27">
+        <v>8000</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>4</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144" s="27">
+        <v>43000</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>5</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145" s="27">
+        <v>25000</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>6</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" s="27">
+        <v>16000</v>
+      </c>
+      <c r="E146" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>7</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" s="27">
+        <v>20000</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D148" s="25"/>
+      <c r="E148" s="21"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D149" s="25">
+        <f>+D150-SUM(D140:D147)</f>
+        <v>162800</v>
+      </c>
+      <c r="E149" s="21"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D150" s="25">
+        <v>305500</v>
+      </c>
+      <c r="E150" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D151" s="25"/>
+      <c r="E151" s="21"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>60</v>
+      </c>
+      <c r="D152" s="25">
+        <v>18000</v>
+      </c>
+      <c r="E152" s="21"/>
+    </row>
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D154" s="25">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D155" s="25">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D156" s="25">
+        <v>8000</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D157" s="25">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D158" s="25">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D159" s="25">
+        <v>18000</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D160" s="25">
+        <v>11000</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D161" s="25">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="162" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D162" s="25">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="163" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D163" s="25">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="164" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D164" s="25">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="165" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D165" s="25">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="166" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D166" s="25">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="167" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D167" s="25">
+        <v>25000</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D168" s="25">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="169" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D169" s="25">
+        <v>16000</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D170" s="25">
+        <v>20000</v>
+      </c>
+      <c r="E170" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" spans="4:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D171" s="22">
+        <f>+SUM(D154:D170)</f>
+        <v>307500</v>
+      </c>
+    </row>
+    <row r="172" spans="4:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D173" s="29">
+        <f>+D150+D152-D137</f>
+        <v>180800</v>
+      </c>
+      <c r="E173" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D174" s="30">
+        <f>+D173-D137</f>
+        <v>38100</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C177" s="10">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D180" s="27">
+        <v>85000</v>
+      </c>
+      <c r="E180" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D181" s="27"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H182" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>1</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183" s="27">
+        <v>24000</v>
+      </c>
+      <c r="E183" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>1</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184" s="27">
+        <v>11000</v>
+      </c>
+      <c r="E184" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D185" s="27">
+        <v>39000</v>
+      </c>
+      <c r="E185" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D186" s="28">
+        <v>11000</v>
+      </c>
+      <c r="E186" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D187" s="4">
+        <f>+SUM(D183:D186)</f>
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D188" s="4"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D189" s="31">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D190" s="31">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D191" s="31">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D192" s="31">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="193" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D193" s="32">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="194" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D194" s="4">
+        <f>+SUM(D189:D193)</f>
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="195" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D195" s="4"/>
+    </row>
+    <row r="196" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D196" s="4">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D197" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="198" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D198" s="32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="199" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D199" s="4">
+        <f>+SUM(D196:D198)</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="201" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D201" s="31">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="202" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D202" s="31">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="203" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D203" s="32">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="204" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D204" s="4">
+        <f>+SUM(D201:D203)</f>
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="206" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D206" s="14">
+        <f>+D194+D199+D204</f>
+        <v>173000</v>
+      </c>
+    </row>
+    <row r="207" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D207" s="29">
+        <f>+D206-D187</f>
+        <v>88000</v>
+      </c>
+      <c r="E207" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C209" s="10">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G212" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H212" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>1</v>
+      </c>
+      <c r="B213" t="s">
+        <v>62</v>
+      </c>
+      <c r="C213">
+        <v>2</v>
+      </c>
+      <c r="D213" s="4">
+        <v>60000</v>
+      </c>
+      <c r="E213" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>1</v>
+      </c>
+      <c r="B214" t="s">
+        <v>47</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214" s="4">
+        <v>41600</v>
+      </c>
+      <c r="E214" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D215" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E215" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D216" s="33">
+        <f>+D213+D214+D215</f>
+        <v>109600</v>
+      </c>
+      <c r="E216" s="4"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C219" s="10">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E222" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G222" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H222" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>1</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E223" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>1</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E224" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D225" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E225" s="4"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D226" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E226" s="4"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D227" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E227" s="4"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D228" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E228" s="4"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D229" s="4">
+        <v>32000</v>
+      </c>
+      <c r="E229" s="4"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D230" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E230" s="4"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D231" s="33">
+        <f>+SUM(D223:D230)</f>
+        <v>147000</v>
+      </c>
+      <c r="E231" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E232" s="4"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C233" s="10">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G236" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H236" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D237" s="4">
+        <v>156000</v>
+      </c>
+      <c r="E237" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D238" s="4"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D239" s="4"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C240" s="10">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D242" s="4">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D243" s="4">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D244" s="4">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D245" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D246" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D247" s="9">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D248" s="9">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D249" s="9">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D250" s="34">
+        <f>+SUM(D242:D249)</f>
+        <v>206000</v>
+      </c>
+    </row>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D251" s="9"/>
+    </row>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D252" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="253" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D253" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="254" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D254" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="255" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D255" s="34">
+        <f>+SUM(D252:D254)</f>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="256" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D256" s="9"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D257" s="9"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D258" s="9">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D259" s="9">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D260" s="9">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D261" s="34">
+        <f>+SUM(D258:D260)</f>
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D262" s="9"/>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D263" s="36">
+        <f>+D250+D255+D261</f>
+        <v>281000</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D266" s="27">
+        <v>20000</v>
+      </c>
+      <c r="E266" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D267" s="35">
+        <f>+D263-D266</f>
+        <v>261000</v>
+      </c>
+      <c r="E267" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="7"/>
+      <c r="B269" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269" s="7"/>
+      <c r="D269" s="7"/>
+      <c r="E269" s="7"/>
+      <c r="G269" s="7"/>
+      <c r="H269" s="7"/>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" s="7"/>
+      <c r="B270" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C270" s="7"/>
+      <c r="D270" s="37">
+        <v>38000</v>
+      </c>
+      <c r="E270" s="7"/>
+      <c r="G270" s="7"/>
+      <c r="H270" s="7"/>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="7"/>
+      <c r="B271" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C271" s="7"/>
+      <c r="D271" s="38">
+        <v>270000</v>
+      </c>
+      <c r="E271" s="7"/>
+      <c r="G271" s="7"/>
+      <c r="H271" s="7"/>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C274" s="10">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D276" s="27">
+        <v>122000</v>
+      </c>
+      <c r="E276" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D277" s="27"/>
+    </row>
+    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D278" s="27"/>
+    </row>
+    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D279" s="27">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D280" s="27">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D281" s="27">
+        <f>8000*(2+2+2+1+2+2+2)</f>
+        <v>104000</v>
+      </c>
+    </row>
+    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D282" s="27"/>
+    </row>
+    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D283" s="27">
+        <v>38000</v>
+      </c>
+      <c r="E283" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D284" s="27">
+        <v>11000</v>
+      </c>
+      <c r="E284" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D285" s="27"/>
+    </row>
+    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D286" s="38">
+        <f>+SUM(D279:D284)</f>
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D287" s="45">
+        <f>+D286-D276</f>
+        <v>63000</v>
+      </c>
+      <c r="E287" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B290" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" s="27"/>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C291" t="s">
+        <v>67</v>
+      </c>
+      <c r="D291" s="27">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C292" t="s">
+        <v>66</v>
+      </c>
+      <c r="D292" s="27">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D293" s="39">
+        <f>+D291+D292</f>
+        <v>98000</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D294" s="27"/>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C297" s="10">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D299" s="27">
+        <v>11000</v>
+      </c>
+      <c r="E299" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D300" s="27"/>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D302" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E302" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G302" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D303" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D304" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D305" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D306" s="4">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D307" s="4">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D308" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D309" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D310" s="4">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D311" s="4">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D312" s="22">
+        <f>+SUM(D303:D311)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D314" s="30">
+        <f>+D312-D299</f>
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C317" s="10">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D319" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G319" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D320" s="42">
+        <v>3000</v>
+      </c>
+      <c r="E320" s="20"/>
+    </row>
+    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D321" s="42">
+        <v>6000</v>
+      </c>
+      <c r="E321" s="20"/>
+    </row>
+    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D322" s="42">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D323" s="42">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D324" s="42">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D325" s="44">
+        <f>+SUM(D320:D324)</f>
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D326" s="42"/>
+    </row>
+    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D327" s="42"/>
+      <c r="G327">
+        <f>1650000/30</f>
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D328" s="42"/>
+    </row>
+    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D329" s="42"/>
+    </row>
+    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C330" s="10">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D331" s="42"/>
+    </row>
+    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D332" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D333" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D334" s="4">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="335" spans="3:7" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="D335" s="43">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="336" spans="3:7" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="D336" s="43">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="337" spans="4:4" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="D337" s="43">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="338" spans="4:4" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="D338" s="43">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="339" spans="4:4" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="D339" s="43">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="340" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D340" s="41">
+        <f>+SUM(D332:D339)</f>
+        <v>140000</v>
       </c>
     </row>
   </sheetData>
